--- a/Calendar.xlsx
+++ b/Calendar.xlsx
@@ -1,67 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Trang tính1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trang tính1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
-  <si>
-    <t>BẢNG BIỂU KẾ HOẠCH</t>
-  </si>
-  <si>
-    <t>Thứ 2</t>
-  </si>
-  <si>
-    <t>Thứ 3</t>
-  </si>
-  <si>
-    <t>Thứ 4</t>
-  </si>
-  <si>
-    <t>Thứ 5</t>
-  </si>
-  <si>
-    <t>Thứ 6</t>
-  </si>
-  <si>
-    <t>Thứ 7</t>
-  </si>
-  <si>
-    <t>Chủ Nhật</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Montserrat"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Montserrat"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -71,32 +43,95 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -294,86 +329,310 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.5"/>
-    <col customWidth="1" min="2" max="2" width="25.25"/>
-    <col customWidth="1" min="3" max="3" width="25.5"/>
-    <col customWidth="1" min="4" max="4" width="25.63"/>
-    <col customWidth="1" min="5" max="5" width="25.38"/>
+    <col width="25.5" customWidth="1" style="3" min="1" max="1"/>
+    <col width="25.25" customWidth="1" style="3" min="2" max="2"/>
+    <col width="25.5" customWidth="1" style="3" min="3" max="3"/>
+    <col width="25.63" customWidth="1" style="3" min="4" max="4"/>
+    <col width="25.38" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BẢNG BIỂU KẾ HOẠCH</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="32.25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
+    <row r="2"/>
+    <row r="3" ht="32.25" customHeight="1" s="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 3</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 5</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 7</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Chủ Nhật</t>
+        </is>
       </c>
     </row>
-    <row r="9" ht="31.5" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>7</v>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>06/07/2026
+(Chưa bắt đầu dự án)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>07/07/2026
+(Chưa bắt đầu dự án)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>08/07/2026
+- Họp khởi động
+- Thu thập yêu cầu (1.1)
+- Phân tích yêu cầu (1.2)
+- Viết tài liệu SRS (1.3)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>09/07/2026
+- Thiết kế Use Case (1.4)
+- Thiết kế ERD (1.5)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>10/07/2026
+- Thiết kế Class (1.6)
+- Thiết kế Activity (1.7)
+- Thiết kế Sequence (1.8)
+- Thiết kế State (1.9)
+- Viết Technical Doc (1.10)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>11/07 - 12/07/2026
+Nghỉ cuối tuần</t>
+        </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9" ht="31.5" customHeight="1" s="3">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 5</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 7</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Chủ Nhật</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>13/07/2026
+- Setup project Backend (2.1)
+- Module Đăng nhập &amp; Security (2.2)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>14/07/2026
+- Module Quản lý Nhân viên (2.3)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>15/07/2026
+- Module Quản lý Bàn (2.4)
+- Module Quản lý Thực đơn (2.5)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>16/07/2026
+- Module Gọi món &amp; Đơn hàng (2.7)
+- Module Kho nguyên liệu (2.6)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>17/07/2026
+- Module Thanh toán &amp; Hóa đơn (2.8)
+- Module Báo cáo thống kê (2.9)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>18/07 - 19/07/2026
+Nghỉ cuối tuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 3</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 5</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 7</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Chủ Nhật</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>20/07/2026
+- Setup React Project (3.1)
+- Auth UI (3.2)
+- Employee UI (3.3)
+- Table UI (3.4)
+- Menu UI (3.5 - P1)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>21/07/2026
+- Menu UI (3.5 - P2)
+- Inventory UI (3.6)
+- Order UI (3.7)
+- Billing UI (3.8)
+- Report UI (3.9)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>22/07/2026
+- Unit &amp; API Testing (4.1, 4.2)
+- Integration Testing (4.3)
+- Sửa lỗi &amp; Hoàn thiện (4.4, 4.5)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>23/07/2026
+(Bàn giao dự án)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>24/07/2026
+(Bàn giao dự án)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>25/07 - 26/07/2026
+Nghỉ cuối tuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="19">
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="D16:D20"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="F10:G14"/>
+    <mergeCell ref="F4:G8"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="E16:E20"/>
     <mergeCell ref="A10:A14"/>
-    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="B16:B20"/>
+    <mergeCell ref="F16:G20"/>
+    <mergeCell ref="D10:D14"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="E10:E14"/>
+    <mergeCell ref="A16:A20"/>
     <mergeCell ref="C10:C14"/>
-    <mergeCell ref="D10:D14"/>
-    <mergeCell ref="E10:E14"/>
-    <mergeCell ref="F10:G14"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="D4:D8"/>
-    <mergeCell ref="E4:E8"/>
-    <mergeCell ref="F4:G8"/>
+    <mergeCell ref="C16:C20"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>